--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D3">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>46</v>
